--- a/光伏配储项目/电价数据/2026/曲江站.xlsx
+++ b/光伏配储项目/电价数据/2026/曲江站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51234</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.72161</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.55011</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5842000000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5137999999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.47941</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43782</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45468</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42711</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42215</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.00023</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42337</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41276</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39165</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41712</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39225</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42088</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41409</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42409</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44291</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27431</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>-0.03801</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.04034</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.04224</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.03747</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.03401</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.03571</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.0466</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.02473</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.02663</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.02575</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>-0.04902</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.04982</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.01788</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>-0.02739</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.02092</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.0447</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.04171</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.03817</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.00886</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.55445</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.39502</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.6807300000000001</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.5709</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43329</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43747</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42438</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5663400000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44951</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6039099999999999</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79835</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6280800000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.63001</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7387</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.92615</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41462</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65973</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58347</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.71976</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.47372</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.62388</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.60349</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.4987799999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.44126</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69159</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.00746</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.63855</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.55663</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.6682100000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49399</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51746</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50461</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5049</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48685</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37434</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.48488</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.5526</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.49336</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42736</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44938</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.26175</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.23605</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.18882</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.17323</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.10966</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.19549</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.23502</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.01507</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.14184</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.03997</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>-0.01384</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.12381</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.18713</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.18344</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.00144</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.04183</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.03661</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.40449</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.40364</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.44311</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.42156</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.42539</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.42405</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40181</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.56953</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.47818</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49305</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.58841</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5315299999999999</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.67135</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6335299999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7191000000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.43835</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.76513</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.47001</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.46866</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43517</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.44468</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43565</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42913</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33471</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50974</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.4262</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.42088</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40875</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38372</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42924</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44491</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44512</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43942</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39527</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.25814</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.25796</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.25018</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20808</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.23029</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27162</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.43225</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.41362</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.4333399999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.46127</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.49703</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.40349</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.45488</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40805</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.4627</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.45088</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.52343</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.52501</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.60829</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.57555</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.59661</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.46322</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42232</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.4816</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.44676</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43626</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45825</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44386</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39511</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34207</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.47409</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39749</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44998</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39251</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26062</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.1261</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.24117</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.19655</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28132</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.19928</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5605800000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.20734</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.21938</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.16503</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.03164</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.02743</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>-0.0107</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.22938</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>-0.008230000000000001</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.02756</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.10088</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.19484</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.19612</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.1031</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.10097</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.10084</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16492</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.40367</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.44812</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39074</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41589</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.20658</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.21584</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.20734</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.20174</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04475</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.21296</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.2089</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.18828</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02863</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.17215</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04207</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04049000000000001</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.0422</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04532</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04199</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04663</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04057</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03828</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.04555</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05803</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.005099999999999999</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03379</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09575</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40965</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46719</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41682</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35081</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6536799999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44525</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42253</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42244</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10252</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20158</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04695000000000001</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04550999999999999</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04784</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04472</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04740999999999999</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04793</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19972</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.1427</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29489</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33532</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40422</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17234</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15859</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15942</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23609</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21398</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28089</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42818</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45648</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41534</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91407</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86248</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29599</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8871100000000001</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6315299999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18669</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86846</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.53654</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33045</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03264</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53038</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79064</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52979</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77263</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77727</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87673</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8736900000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49283</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39948</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44957</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20658</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87881</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6214400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53822</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49757</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45576</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43707</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41458</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43354</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5856</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42718</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5956399999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6013500000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6905399999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46848</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41766</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5803400000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.21484</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8580399999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.7684</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.7651</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.21563</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44052</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.53572</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.26678</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40961</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45182</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41458</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35333</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9181</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46463</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40786</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46392</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40948</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49931</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38731</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16601</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26219</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19891</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19292</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28277</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25561</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44323</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42317</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42005</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59549</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8897999999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.4468</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16102</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6999099999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79075</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66465</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5794900000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45066</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50104</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44023</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43754</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41316</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42358</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50051</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41316</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.4344</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43453</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45029</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42379</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43401</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41316</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41319</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42338</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49467</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5498200000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24964</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15274</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27779</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02085</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26162</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25528</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28296</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.4036</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5699299999999999</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46221</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.84873</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46446</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.45502</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38524</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32341</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42177</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39818</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28021</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27901</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.2251</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14117</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14492</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.2799</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14126</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13592</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.2468</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13642</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.14428</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10759</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10721</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.12541</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13551</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14035</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27596</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.3973</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44867</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40063</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39639</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45161</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43864</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43796</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44374</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40186</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39705</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34826</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5373300000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46771</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42288</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41501</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.12347</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.10459</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20018</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.14333</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24322</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24225</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28581</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25983</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41496</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35993</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41736</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43528</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42583</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.46148</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5081</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24964</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27204</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.20137</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.28048</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.45734</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.11043</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.44817</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41475</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.68976</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50968</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2218</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31326</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.16536</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.09995999999999999</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.15368</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.19231</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.19194</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.28201</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.19507</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34952</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.15552</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>-0.04848</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>-0.04989</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>-0.04951</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.15174</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38437</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41825</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41137</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.77037</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45183</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45759</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34427</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41095</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26557</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14847</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>-0.04921</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19971</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27977</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28027</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21624</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25529</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.2849100000000001</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27712</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28986</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.22437</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43283</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6417200000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.59914</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.60722</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48767</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.81433</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.4879</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.81501</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44546</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.49034</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40145</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47178</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41863</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35989</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48868</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47964</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48256</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41629</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39684</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40231</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40957</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40756</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41587</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39837</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40802</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.37484</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41654</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>-0.04807</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.4094100000000001</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44604</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43794</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>-0.01926</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>-0.02058</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>-0.04813</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>-0.04418</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>-0.04788000000000001</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>-0.03931</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.11932</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.16649</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>-0.04204</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.03818999999999999</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.1846</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.18074</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.18692</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43616</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.4921</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.4382</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50336</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50624</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.54464</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6924</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7136399999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.9285800000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.55333</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80664</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58257</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52508</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8318300000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77003</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6234299999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67211</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44134</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47173</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48185</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47632</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46905</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41683</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55138</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4275</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44126</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45517</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43407</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42405</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44501</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39864</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45416</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40407</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.25082</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.19938</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.24942</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.25014</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.24868</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.18945</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>-0.03466</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.19655</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>-0.04675</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.0482</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.04143</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>-0.04246</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>-0.01009</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>-0.04904</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.18399</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.20104</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.20088</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.20279</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43292</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4158</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41502</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40898</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40944</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39617</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39496</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.3653</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44403</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.25003</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.24975</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.24993</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.24984</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22596</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22974</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.20693</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.2491</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.22102</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13975</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.2435</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.20288</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.19651</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25009</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.20976</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16915</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18733</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.22295</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23377</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22759</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.18768</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.16875</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.17773</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.14446</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.17948</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.18963</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.13525</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.17951</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.18274</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.33648</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.22413</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.21667</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.21669</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.22374</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.20556</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.19331</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04946</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.04952</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.03867</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04142</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03895000000000001</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04786</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.04720000000000001</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03856</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00067</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.25238</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02164</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03774</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19017</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.24797</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.21432</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.22631</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.21412</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.21282</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.24826</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.22564</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.22568</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.28891</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.13398</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.22305</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5320900000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.21026</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.26178</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.24846</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.27624</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.28636</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.28936</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26492</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28769</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.26833</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.25606</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.62459</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.75729</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.7497200000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.5727899999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.23121</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.02973</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.22559</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17503</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.19802</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.19764</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.17169</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.04875</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04846</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.20613</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.20671</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.01439</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.17769</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.18976</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.18493</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.15741</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2566000000000001</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.20396</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25621</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.25726</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.25675</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.42474</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32156</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.13249</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.52074</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.53163</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41542</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.28285</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41868</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.1689</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.20766</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.08559</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37667</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>-0.04804</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>-0.04679</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>-0.04595</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.1998</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14178</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27691</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.20462</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.29201</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.16376</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.20504</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.20546</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.18926</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.28206</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.27409</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.42422</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42645</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34089</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.8509500000000001</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.39666</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.39787</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36739</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.54857</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.19325</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.18933</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.19243</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.15489</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.24232</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.15295</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>-0.04635</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>-0.04301</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.19872</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>-0.04287</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.14313</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.14029</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.15665</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>-0.04152</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>-0.04172</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>-0.04301</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>-0.04322</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.12652</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>-0.04299</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.18325</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.13574</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.19631</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.45471</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.44256</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.4368</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41426</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.27612</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31849</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.26545</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.13831</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.27152</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.2585</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.25569</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.19905</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.26747</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.19938</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.13348</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.16864</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.16335</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.20231</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.27012</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.44759</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.19476</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.19013</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.13941</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>-0.03513</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>-0.04545</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>-0.0443</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.16963</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.20836</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>-0.0476</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>-0.04536</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>-0.04541</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.15836</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.20654</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.19811</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.20814</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>-0.03602</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.15862</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.20923</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>-0.03663</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.18492</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.26907</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.27614</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38614</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.40939</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.74454</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32626</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.20649</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.27317</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.18114</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.24547</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.27877</v>
+      </c>
+      <c r="T141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.18777</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.18599</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.19804</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.29851</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.28958</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.19899</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.19888</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.19295</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.19856</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>-0.04272</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.19301</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.26957</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.20531</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.16472</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.03288</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.03847</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.21029</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>-0.03087</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.16924</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.01575</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.02437</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.03322</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.04749</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01837</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.03528</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.03581</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.005900000000000001</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.01587</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.22184</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08723</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>-0.00523</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>-0.03188</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>-0.02953</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>-0.0354</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>-0.03677</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>-0.03562</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>-0.03127</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>-0.03372</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.19875</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.21195</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>-0.03042</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>-0.03006</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.16051</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.13825</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.2205</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.18786</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.21975</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.26685</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.17538</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.17724</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.17849</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.11682</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.17247</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.18785</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.45837</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.18073</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.29918</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.18519</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.19889</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.19921</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.19368</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.18837</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>-0.04164</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.20894</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.16855</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.17859</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>-0.04042</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>-0.03897999999999999</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.14994</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>-0.02359</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>-0.04739</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.49754</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.21547</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.19608</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.20902</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.28398</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.27083</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37232</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38404</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.50562</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37645</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.17821</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.31767</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.28866</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.28891</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.2711</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.26776</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.18439</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.14007</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.18777</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.18705</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.16709</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.1883</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.19274</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.19326</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1218</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.20876</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.19789</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.15297</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.17491</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.19638</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.18997</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.18553</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.19134</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.20536</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38556</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40155</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47471</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38746</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37679</v>
       </c>
     </row>
   </sheetData>
